--- a/logs_export.xlsx
+++ b/logs_export.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,41 +417,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>username</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>total_rows</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>valid_rows</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>invalid_rows</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
@@ -471,92 +459,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>shaurya kalra</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cleaned file SalesQL_contact_export-2025-12-16- 89.xlsx</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>88</v>
-      </c>
-      <c r="E2" t="n">
-        <v>88</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>46033.00543981481</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>shaurya kalra</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>Logged in</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>46033.00519675926</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>shaurya kalra</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Logged in</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>46031.92048611111</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>shaurya kalra</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Logged in</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>46029.5780787037</v>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" s="1" t="n">
+        <v>46178.42165509259</v>
       </c>
     </row>
   </sheetData>
